--- a/Configs/source/Datas/special.xlsx
+++ b/Configs/source/Datas/special.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="29100" windowHeight="12700"/>
   </bookViews>
   <sheets>
-    <sheet name="Mengpo" sheetId="1" r:id="rId1"/>
+    <sheet name="MengpoTable" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1126,7 +1126,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
@@ -1160,7 +1160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" spans="1:8">
+    <row r="3" s="3" customFormat="1" spans="1:7">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1171,7 +1171,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:8">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1182,7 +1182,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="4:8">
       <c r="D8" t="s">
         <v>12</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="4:8">
       <c r="D9" t="s">
         <v>12</v>
       </c>
@@ -1237,7 +1237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="4:8">
       <c r="D10" t="s">
         <v>12</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="6:8">
       <c r="F11" t="s">
         <v>16</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="2:8">
       <c r="B12" t="s">
         <v>8</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="2:8">
       <c r="B13" t="s">
         <v>8</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="2:8">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="2:8">
       <c r="B15" t="s">
         <v>8</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="2:8">
       <c r="B16" t="s">
         <v>8</v>
       </c>

--- a/Configs/source/Datas/special.xlsx
+++ b/Configs/source/Datas/special.xlsx
@@ -32,55 +32,55 @@
     <t>##var</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>mengpo_soup_effect</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
+    <t>CardEnum</t>
+  </si>
+  <si>
     <t>map,CardTypeEnum,int</t>
   </si>
   <si>
-    <t>CardEnum</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
     <t>##</t>
   </si>
   <si>
+    <t>孟婆汤_攻击一</t>
+  </si>
+  <si>
     <t>攻击</t>
   </si>
   <si>
-    <t>孟婆汤_攻击一</t>
-  </si>
-  <si>
     <t>孟婆汤_攻击二</t>
   </si>
   <si>
     <t>孟婆汤_攻击三</t>
   </si>
   <si>
+    <t>孟婆汤_功能一</t>
+  </si>
+  <si>
     <t>功能</t>
   </si>
   <si>
-    <t>孟婆汤_功能一</t>
-  </si>
-  <si>
     <t>孟婆汤_功能二</t>
   </si>
   <si>
     <t>孟婆汤_功能三</t>
   </si>
   <si>
+    <t>孟婆汤_请神</t>
+  </si>
+  <si>
     <t>请神</t>
-  </si>
-  <si>
-    <t>孟婆汤_请神</t>
   </si>
   <si>
     <t>孟婆汤_AF平衡药水_1</t>
@@ -1125,608 +1125,608 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" s="2" customFormat="1" spans="1:8">
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" s="2" customFormat="1" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
-      <c r="H2" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" s="3" customFormat="1" spans="1:7">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" s="3" customFormat="1" spans="1:9">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-    </row>
-    <row r="5" spans="2:8">
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="2:5">
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
       <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="H6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
+    </row>
+    <row r="7" spans="2:5">
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
         <v>3</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="4:8">
-      <c r="D8" t="s">
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="4:8">
-      <c r="D9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9">
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="4:8">
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10">
+    </row>
+    <row r="10" spans="2:7">
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="6:8">
-      <c r="F11" t="s">
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" t="s">
         <v>16</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12" spans="2:8">
+      <c r="I11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
       <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
       <c r="B13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13">
         <v>2</v>
       </c>
-      <c r="H13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
+    </row>
+    <row r="14" spans="2:7">
       <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
         <v>3</v>
       </c>
-      <c r="H14" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8">
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
       <c r="B16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16">
         <v>2</v>
       </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
       <c r="H16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17">
         <v>3</v>
       </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
       <c r="H17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18">
         <v>2</v>
       </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
-      <c r="H19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20">
+        <v>26</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20">
         <v>2</v>
       </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20">
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
         <v>3</v>
       </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8">
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21">
         <v>2</v>
       </c>
-      <c r="D21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>2</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23">
         <v>2</v>
       </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23">
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
         <v>3</v>
       </c>
-      <c r="F23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
       <c r="H23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24">
         <v>3</v>
       </c>
-      <c r="D24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25">
         <v>3</v>
       </c>
-      <c r="D25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25">
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
         <v>2</v>
       </c>
-      <c r="H25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E26">
         <v>3</v>
       </c>
-      <c r="H26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8">
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27">
+        <v>33</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27">
         <v>3</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
       <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28">
         <v>3</v>
       </c>
-      <c r="D28" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28">
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28">
         <v>2</v>
       </c>
-      <c r="F28" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
       <c r="H28" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
       <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E29">
         <v>3</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
       <c r="B30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-      <c r="F30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30">
+        <v>36</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31">
         <v>2</v>
       </c>
-      <c r="F31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
       <c r="H31" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
+        <v>17</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32">
+        <v>38</v>
+      </c>
+      <c r="D32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32">
         <v>3</v>
       </c>
-      <c r="F32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
       <c r="H32" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="33" spans="4:8">
-      <c r="D33" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33" t="s">
+        <v>39</v>
       </c>
       <c r="F33" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="34" spans="4:8">
-      <c r="D34" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34">
+        <v>17</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34">
         <v>2</v>
       </c>
-      <c r="F34" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
       <c r="H34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="4:8">
-      <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35">
+        <v>17</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35">
         <v>3</v>
       </c>
-      <c r="F35" t="s">
-        <v>16</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
       <c r="H35" t="s">
-        <v>41</v>
+        <v>17</v>
+      </c>
+      <c r="I35">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
